--- a/Output/PowerPoint_Figures/Fig_S3/Fig_S3a_data.xlsx
+++ b/Output/PowerPoint_Figures/Fig_S3/Fig_S3a_data.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,49 +418,49 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Equation</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Accuracy</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>AUC</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>N_samples</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Confusion_Matrix</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -506,12 +494,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Performance_Metrics/loocv_results.csv</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" t="n">
         <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -545,12 +533,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Performance_Metrics/loocv_results.csv</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" t="n">
         <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -584,12 +572,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Performance_Metrics/loocv_results.csv</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" t="n">
         <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -623,12 +611,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Performance_Metrics/loocv_results.csv</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" t="n">
         <v>4</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -662,12 +650,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Performance_Metrics/loocv_results.csv</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" t="n">
         <v>5</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -701,12 +689,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Performance_Metrics/loocv_results.csv</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" t="n">
         <v>6</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -740,12 +728,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Performance_Metrics/loocv_results.csv</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" t="n">
         <v>7</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -779,12 +767,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Performance_Metrics/loocv_results.csv</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" t="n">
         <v>8</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -818,12 +806,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Performance_Metrics/loocv_results.csv</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" t="n">
         <v>9</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -857,12 +845,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Performance_Metrics/loocv_results.csv</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" t="n">
         <v>10</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -896,12 +884,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Performance_Metrics/loocv_results.csv</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" t="n">
         <v>11</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -935,12 +923,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Performance_Metrics/loocv_results.csv</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" t="n">
         <v>12</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -974,12 +962,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Performance_Metrics/loocv_results.csv</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" t="n">
         <v>13</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -1013,12 +1001,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Performance_Metrics/loocv_results.csv</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" t="n">
         <v>14</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -1052,12 +1040,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Performance_Metrics/loocv_results.csv</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" t="n">
         <v>15</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -1091,12 +1079,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Performance_Metrics/loocv_results.csv</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" t="n">
         <v>16</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -1130,12 +1118,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Performance_Metrics/loocv_results.csv</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" t="n">
         <v>17</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -1169,12 +1157,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Performance_Metrics/loocv_results.csv</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" t="n">
         <v>18</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -1208,12 +1196,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Performance_Metrics/loocv_results.csv</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" t="n">
         <v>19</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -1247,12 +1235,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Performance_Metrics/loocv_results.csv</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" t="n">
         <v>20</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -1286,12 +1274,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Performance_Metrics/loocv_results.csv</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" t="n">
         <v>21</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -1325,12 +1313,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Performance_Metrics/loocv_results.csv</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" t="n">
         <v>22</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -1364,12 +1352,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Performance_Metrics/loocv_results.csv</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" t="n">
         <v>23</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -1403,12 +1391,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Performance_Metrics/loocv_results.csv</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" t="n">
         <v>24</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -1442,12 +1430,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Performance_Metrics/loocv_results.csv</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" t="n">
         <v>25</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -1481,12 +1469,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Performance_Metrics/loocv_results.csv</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" t="n">
         <v>26</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -1520,12 +1508,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Performance_Metrics/loocv_results.csv</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" t="n">
         <v>27</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -1559,12 +1547,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Performance_Metrics/loocv_results.csv</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" t="n">
         <v>28</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -1598,12 +1586,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Performance_Metrics/loocv_results.csv</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" t="n">
         <v>29</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -1637,12 +1625,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Performance_Metrics/loocv_results.csv</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" t="n">
         <v>30</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -1676,12 +1664,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Performance_Metrics/loocv_results.csv</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" t="n">
         <v>31</v>
       </c>
       <c r="B33" t="inlineStr">
@@ -1715,12 +1703,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Performance_Metrics/loocv_results.csv</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" t="n">
         <v>32</v>
       </c>
       <c r="B34" t="inlineStr">
@@ -1754,12 +1742,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Performance_Metrics/loocv_results.csv</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" t="n">
         <v>33</v>
       </c>
       <c r="B35" t="inlineStr">
@@ -1793,12 +1781,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Performance_Metrics/loocv_results.csv</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" t="n">
         <v>34</v>
       </c>
       <c r="B36" t="inlineStr">
@@ -1832,12 +1820,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Performance_Metrics/loocv_results.csv</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" t="n">
         <v>35</v>
       </c>
       <c r="B37" t="inlineStr">
@@ -1871,7 +1859,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Performance_Metrics/loocv_results.csv</t>
         </is>
       </c>
     </row>
@@ -1890,44 +1878,44 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Equation</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Accuracy</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>AUC</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>N_samples</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Confusion_Matrix</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -1961,7 +1949,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" t="n">
         <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -1995,7 +1983,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -2029,7 +2017,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -2063,7 +2051,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -2097,7 +2085,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" t="n">
         <v>7</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -2131,7 +2119,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" t="n">
         <v>8</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -2165,7 +2153,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" t="n">
         <v>9</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -2199,7 +2187,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" t="n">
         <v>11</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -2233,7 +2221,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" t="n">
         <v>12</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -2267,7 +2255,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" t="n">
         <v>13</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -2301,7 +2289,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" t="n">
         <v>15</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -2335,7 +2323,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" t="n">
         <v>16</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -2369,7 +2357,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" t="n">
         <v>17</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -2403,7 +2391,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" t="n">
         <v>19</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -2437,7 +2425,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" t="n">
         <v>20</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -2471,7 +2459,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" t="n">
         <v>21</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -2505,7 +2493,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" t="n">
         <v>23</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -2539,7 +2527,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" t="n">
         <v>24</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -2573,7 +2561,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" t="n">
         <v>25</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -2607,7 +2595,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" t="n">
         <v>27</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -2641,7 +2629,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" t="n">
         <v>28</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -2675,7 +2663,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" t="n">
         <v>29</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -2709,7 +2697,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" t="n">
         <v>31</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -2743,7 +2731,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" t="n">
         <v>32</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -2777,7 +2765,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" t="n">
         <v>33</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -2811,7 +2799,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" t="n">
         <v>35</v>
       </c>
       <c r="B28" t="inlineStr">
